--- a/output/pdf_financials_xlsx/VMET.xlsx
+++ b/output/pdf_financials_xlsx/VMET.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.148</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.267</v>
       </c>
     </row>
     <row r="13">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.874</v>
+        <v>-1.022</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>29.602</v>
+        <v>29.335</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.874</v>
+        <v>-1.022</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>29.602</v>
+        <v>29.335</v>
       </c>
     </row>
     <row r="30">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-8.750500600720864</v>
+        <v>-10.23227873448138</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>142.9979228056616</v>
+        <v>141.708130042027</v>
       </c>
     </row>
     <row r="31">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">

--- a/output/pdf_financials_xlsx/VMET.xlsx
+++ b/output/pdf_financials_xlsx/VMET.xlsx
@@ -2976,7 +2976,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>-2.448</v>
       </c>
